--- a/assets/data/excel/elementRelations.xlsx
+++ b/assets/data/excel/elementRelations.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="元素克制" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="elementRelations" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,35 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +68,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,115 +446,124 @@
   </sheetPr>
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>element</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>elementName</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>elementNameEn</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>strongAgainst</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>weakAgainst</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>bonusMultiplier</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>resistMultiplier</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>元素ID</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>元素名称</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>元素英文名</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>英文名称</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>克制元素</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>被克制元素</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>克制伤害加成</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>被克制伤害减免</t>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>克制伤害倍率</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>被克制伤害倍率</t>
         </is>
       </c>
     </row>
@@ -629,27 +669,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>光</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>dark</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>暗</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Dark</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -662,27 +702,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>dark</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>暗</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dark</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>light</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>光</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>dark</t>
-        </is>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="F8" t="n">

--- a/assets/data/excel/elementRelations.xlsx
+++ b/assets/data/excel/elementRelations.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -651,7 +651,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>light</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -717,12 +717,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>water</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>light</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>wind</t>
         </is>
       </c>
       <c r="F8" t="n">

--- a/assets/data/excel/elementRelations.xlsx
+++ b/assets/data/excel/elementRelations.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>wind</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -651,7 +651,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>water</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>wind</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -717,7 +717,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>light</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
